--- a/templates/standard_survey_settings.xlsx
+++ b/templates/standard_survey_settings.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항설정" sheetId="1" r:id="Rf0bc4cdb36af439f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="배너설정" sheetId="2" r:id="Rdfbde32993a440f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성가이드" sheetId="3" r:id="R629054b37ffc4fe8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항설정" sheetId="1" r:id="R5a87f87c3dd34672"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="배너설정" sheetId="2" r:id="Rb92f039e8eb440ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성가이드" sheetId="3" r:id="R5b866e92cfdb4918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그래프설정" sheetId="4" r:id="Rb6137a44ad1e4a3f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -49,7 +50,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -66,6 +67,11 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -74,7 +80,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -142,6 +148,15 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -303,6 +318,7 @@
     <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -320,6 +336,9 @@
       </x:c>
       <x:c r="E1" s="6" t="str">
         <x:v>배너설정</x:v>
+      </x:c>
+      <x:c r="F1" s="34" t="str">
+        <x:v>문항영역</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -18092,4 +18111,52 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="35" t="str">
+        <x:v>문항번호</x:v>
+      </x:c>
+      <x:c r="B1" s="35" t="str">
+        <x:v>막대색상</x:v>
+      </x:c>
+      <x:c r="C1" s="35" t="str">
+        <x:v>줄바꿈</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>Q1</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>#406A9F</x:v>
+      </x:c>
+      <x:c r="C2" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Q2</x:v>
+      </x:c>
+      <x:c r="B3" t="str"/>
+      <x:c r="C3" t="str">
+        <x:v>매우 만족=&gt;매우|만족;전혀 만족하지 않음=&gt;전혀 만족하지|않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str"/>
+      <x:c r="B4" t="str"/>
+      <x:c r="C4" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>